--- a/contenus/tab2/exs10-cas-combine-tableau-de-bord.xlsx
+++ b/contenus/tab2/exs10-cas-combine-tableau-de-bord.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consignes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercice" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1232,655 +1231,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Quantité en stock</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Seuil d'alerte</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Désignation</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Catégorie</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Prix unitaire (€)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Valeur du stock (€)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REF401</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D2">
-        <f>VLOOKUP(A2,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E2">
-        <f>VLOOKUP(A2,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F2">
-        <f>VLOOKUP(A2,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G2">
-        <f>B2*F2</f>
-        <v/>
-      </c>
-      <c r="H2">
-        <f>IF(B2&lt;C2,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>REF401</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Casque de chantier</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REF402</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
-      <c r="D3">
-        <f>VLOOKUP(A3,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E3">
-        <f>VLOOKUP(A3,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F3">
-        <f>VLOOKUP(A3,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G3">
-        <f>B3*F3</f>
-        <v/>
-      </c>
-      <c r="H3">
-        <f>IF(B3&lt;C3,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>REF402</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Gants de manutention</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REF403</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <f>VLOOKUP(A4,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>VLOOKUP(A4,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>VLOOKUP(A4,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>B4*F4</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>IF(B4&lt;C4,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>REF403</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Chaussures de sécurité</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REF405</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>200</v>
-      </c>
-      <c r="C5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5">
-        <f>VLOOKUP(A5,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E5">
-        <f>VLOOKUP(A5,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>VLOOKUP(A5,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>B5*F5</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>IF(B5&lt;C5,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>REF404</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Lunettes de protection</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REF406</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <f>VLOOKUP(A6,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>VLOOKUP(A6,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>VLOOKUP(A6,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>B6*F6</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>IF(B6&lt;C6,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>REF405</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Carton simple cannelure</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REF407</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>50</v>
-      </c>
-      <c r="C7" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <f>VLOOKUP(A7,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>VLOOKUP(A7,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>VLOOKUP(A7,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>B7*F7</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>IF(B7&lt;C7,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>REF406</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Film étirable</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REF409</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <f>VLOOKUP(A8,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>VLOOKUP(A8,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>VLOOKUP(A8,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>B8*F8</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>IF(B8&lt;C8,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>REF407</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Étiquette code-barres</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REF410</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9">
-        <f>VLOOKUP(A9,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>VLOOKUP(A9,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F9">
-        <f>VLOOKUP(A9,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>B9*F9</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>IF(B9&lt;C9,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>REF408</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Palette Europe</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REF411</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>80</v>
-      </c>
-      <c r="C10" t="n">
-        <v>40</v>
-      </c>
-      <c r="D10">
-        <f>VLOOKUP(A10,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>VLOOKUP(A10,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>VLOOKUP(A10,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>B10*F10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>IF(B10&lt;C10,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>REF409</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Transpalette manuel</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REF412</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <f>VLOOKUP(A11,$J$2:$M$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>VLOOKUP(A11,$J$2:$M$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>VLOOKUP(A11,$J$2:$M$13,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>B11*F11</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>IF(B11&lt;C11,"À commander","OK")</f>
-        <v/>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>REF410</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Diable pliant</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>REF411</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Sangle d'arrimage</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>REF412</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Chariot de manutention</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Catégorie</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Valeur totale</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="B15">
-        <f>SUMIF(E2:E11,A15,G2:G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="B16">
-        <f>SUMIF(E2:E11,A16,G2:G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-      <c r="B17">
-        <f>SUMIF(E2:E11,A17,G2:G11)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>